--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486783_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486783_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.252000000000001</v>
+        <v>8.2659</v>
       </c>
       <c r="E2" t="n">
-        <v>9.514900000000001</v>
+        <v>8.901300000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2629</v>
+        <v>-0.6354</v>
       </c>
       <c r="G2" t="n">
         <v>6.4812</v>
@@ -610,13 +610,13 @@
         <v>1.3515</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4272</v>
+        <v>1.4412</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5165</v>
+        <v>0.9029</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9107</v>
+        <v>0.5383</v>
       </c>
       <c r="V2" t="n">
         <v>-0.0426</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2771</v>
+        <v>3.4772</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7319</v>
+        <v>3.4286</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5452</v>
+        <v>0.0485</v>
       </c>
       <c r="G3" t="n">
         <v>2.6869</v>
@@ -688,13 +688,13 @@
         <v>1.1585</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6481</v>
+        <v>1.8482</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9926</v>
+        <v>0.6892</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6556</v>
+        <v>1.1589</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2856</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2152</v>
+        <v>2.9049</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5316</v>
+        <v>2.2213</v>
       </c>
       <c r="F4" t="n">
         <v>0.6836</v>
@@ -766,10 +766,10 @@
         <v>0.5792</v>
       </c>
       <c r="S4" t="n">
-        <v>0.855</v>
+        <v>0.5448</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3859</v>
+        <v>0.0757</v>
       </c>
       <c r="U4" t="n">
         <v>0.4691</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1354</v>
+        <v>1.3244</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7032</v>
+        <v>0.917</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4322</v>
+        <v>0.4074</v>
       </c>
       <c r="G5" t="n">
         <v>-4.5694</v>
@@ -844,13 +844,13 @@
         <v>1.1585</v>
       </c>
       <c r="S5" t="n">
-        <v>0.535</v>
+        <v>0.724</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0824</v>
+        <v>0.2961</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4527</v>
+        <v>0.4278</v>
       </c>
       <c r="V5" t="n">
         <v>4.0113</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. HERNÁNDEZ CHÁVEZ</t>
+          <t>S. SOW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8783</v>
+        <v>1.0295</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2077</v>
+        <v>0.5263</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3293</v>
+        <v>0.5032</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2636</v>
+        <v>0.3163</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2835</v>
+        <v>-0.0069</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5471</v>
+        <v>0.3232</v>
       </c>
       <c r="J6" t="n">
-        <v>0.958</v>
+        <v>0.1028</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5254</v>
+        <v>0.0621</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5674</v>
+        <v>0.0407</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2215</v>
+        <v>0.2135</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2418</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0203</v>
+        <v>0.2826</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1931</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1585</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9488</v>
+        <v>0.4276</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3583</v>
+        <v>0.1379</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5906</v>
+        <v>0.2897</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8568</v>
+        <v>0.2856</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. SOW</t>
+          <t>A. BRASSEUR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8557</v>
+        <v>0.8355</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5263</v>
+        <v>1.6528</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3294</v>
+        <v>-0.8172</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3163</v>
+        <v>0.3627</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0069</v>
+        <v>-1.8348</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3232</v>
+        <v>2.1975</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1028</v>
+        <v>1.8047</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0621</v>
+        <v>-0.5239</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0407</v>
+        <v>2.3286</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2135</v>
+        <v>-1.442</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-1.3109</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2826</v>
+        <v>-0.1311</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.5792</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.5792</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2538</v>
+        <v>0.1793</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1379</v>
+        <v>-0.1519</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1159</v>
+        <v>0.3312</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2856</v>
+        <v>-0.2856</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BRASSEUR</t>
+          <t>R. HERNÁNDEZ CHÁVEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3804</v>
+        <v>0.5984</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4459</v>
+        <v>0.9526</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0655</v>
+        <v>-0.3542</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3627</v>
+        <v>-0.2636</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.8348</v>
+        <v>0.2835</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1975</v>
+        <v>-0.5471</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8047</v>
+        <v>0.958</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5239</v>
+        <v>1.5254</v>
       </c>
       <c r="L8" t="n">
-        <v>2.3286</v>
+        <v>-0.5674</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.442</v>
+        <v>-1.2215</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3109</v>
+        <v>-1.2418</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1311</v>
+        <v>0.0203</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5792</v>
+        <v>0.1931</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5792</v>
+        <v>1.1585</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2759</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3587</v>
+        <v>0.1032</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0828</v>
+        <v>0.5657</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.8568</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2856</v>
+        <v>-0.8568</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.794</v>
+        <v>-0.052</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5313</v>
+        <v>-0.0625</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2626</v>
+        <v>0.0105</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7455000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>0.3862</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.149</v>
+        <v>0.593</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2484</v>
+        <v>0.2205</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0994</v>
+        <v>0.3725</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2856</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4105</v>
+        <v>-1.0698</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4962</v>
+        <v>-0.1308</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9142</v>
+        <v>-0.9391</v>
       </c>
       <c r="G10" t="n">
         <v>0.8</v>
@@ -1234,13 +1234,13 @@
         <v>1.3515</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3422</v>
+        <v>0.6828</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3864</v>
+        <v>-0.0209</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7286</v>
+        <v>0.7037</v>
       </c>
       <c r="V10" t="n">
         <v>-0.0426</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. DIAZ FELST</t>
+          <t>M. GONZALEZ-MONJE PEREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6024</v>
+        <v>-1.1131</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3466</v>
+        <v>-0.0436</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2558</v>
+        <v>-1.0695</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0918</v>
+        <v>-1.9959</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5175999999999999</v>
+        <v>0.3031</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5742</v>
+        <v>-2.2991</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0673</v>
+        <v>-0.223</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1035</v>
+        <v>0.9932</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0361</v>
+        <v>-1.2162</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1591</v>
+        <v>-1.773</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6211</v>
+        <v>-0.6901</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5381</v>
+        <v>-1.0829</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5792</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5187</v>
+        <v>0.2344</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4139</v>
+        <v>-0.083</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1047</v>
+        <v>0.3174</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5712</v>
+        <v>1.2277</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. GONZALEZ-MONJE PEREZ</t>
+          <t>M. DIAZ FELST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6564</v>
+        <v>-1.2218</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5125</v>
+        <v>-0.1397</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.144</v>
+        <v>-1.082</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.9959</v>
+        <v>-1.0918</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3031</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.2991</v>
+        <v>-0.5742</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.223</v>
+        <v>0.0673</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9932</v>
+        <v>0.1035</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2162</v>
+        <v>-0.0361</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.773</v>
+        <v>-1.1591</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6901</v>
+        <v>-0.6211</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0829</v>
+        <v>-0.5381</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.5792</v>
+        <v>0.5792</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3862</v>
+        <v>0.5792</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.309</v>
+        <v>-0.138</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5518</v>
+        <v>-0.2071</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2429</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2277</v>
+        <v>-0.5712</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.0627</v>
+        <v>-1.9593</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6281</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="F13" t="n">
         <v>-1.4346</v>
@@ -1468,10 +1468,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>0.1034</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>0.1034</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.4681</v>
+        <v>13.0198</v>
       </c>
       <c r="E14" t="n">
-        <v>17.1468</v>
+        <v>17.6986</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.6785</v>
+        <v>-4.678800000000001</v>
       </c>
       <c r="G14" t="n">
         <v>1.656500000000001</v>
@@ -1516,7 +1516,7 @@
         <v>1.0347</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6216999999999995</v>
+        <v>0.6216999999999993</v>
       </c>
       <c r="J14" t="n">
         <v>15.9404</v>
@@ -1543,16 +1543,16 @@
         <v>-8.688600000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>8.688499999999999</v>
+        <v>8.688500000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>6.757500000000001</v>
+        <v>7.309600000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5144</v>
+        <v>2.066</v>
       </c>
       <c r="U14" t="n">
-        <v>5.2436</v>
+        <v>5.243399999999999</v>
       </c>
       <c r="V14" t="n">
         <v>4.054</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6659</v>
+        <v>2.6382</v>
       </c>
       <c r="E15" t="n">
-        <v>4.091</v>
+        <v>4.4013</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.4251</v>
+        <v>-1.7631</v>
       </c>
       <c r="G15" t="n">
         <v>0.9992</v>
@@ -1624,13 +1624,13 @@
         <v>1.7377</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.1515</v>
+        <v>-1.1792</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4624</v>
+        <v>-1.1521</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6891</v>
+        <v>-0.0271</v>
       </c>
       <c r="V15" t="n">
         <v>3.3975</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. SOUSA SILVA</t>
+          <t>S. KONTE SYLLA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1308</v>
+        <v>1.364</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2444</v>
+        <v>3.9304</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1137</v>
+        <v>-2.5663</v>
       </c>
       <c r="G16" t="n">
-        <v>0.786</v>
+        <v>2.1804</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3511</v>
+        <v>2.3455</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1371</v>
+        <v>-0.1651</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4625</v>
+        <v>5.0985</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2011</v>
+        <v>3.7941</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2615</v>
+        <v>1.3044</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6766</v>
+        <v>-2.9181</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5522</v>
+        <v>-1.4486</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1244</v>
+        <v>-1.4695</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1931</v>
+        <v>0.9654</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.1931</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3862</v>
+        <v>1.1585</v>
       </c>
       <c r="S16" t="n">
-        <v>0.48</v>
+        <v>-1.0827</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3032</v>
+        <v>-0.8899</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1768</v>
+        <v>-0.1928</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3282</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3282</v>
+        <v>-0.0852</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. KONTE SYLLA</t>
+          <t>A. SOUSA SILVA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0841</v>
+        <v>0.8991</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8269</v>
+        <v>1.0376</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.7428</v>
+        <v>-0.1385</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1804</v>
+        <v>0.786</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3455</v>
+        <v>-0.3511</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1651</v>
+        <v>1.1371</v>
       </c>
       <c r="J17" t="n">
-        <v>5.0985</v>
+        <v>1.4625</v>
       </c>
       <c r="K17" t="n">
-        <v>3.7941</v>
+        <v>0.2011</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3044</v>
+        <v>1.2615</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.9181</v>
+        <v>-0.6766</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4486</v>
+        <v>-0.5522</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4695</v>
+        <v>-0.1244</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.1931</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1585</v>
+        <v>0.3862</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3626</v>
+        <v>0.2483</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9933</v>
+        <v>0.0964</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3693</v>
+        <v>0.1519</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6991000000000001</v>
+        <v>-0.3282</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.0852</v>
+        <v>-0.3282</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6338</v>
+        <v>-0.5649</v>
       </c>
       <c r="E18" t="n">
-        <v>0.915</v>
+        <v>0.7081</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5488</v>
+        <v>-1.273</v>
       </c>
       <c r="G18" t="n">
         <v>1.2586</v>
@@ -1858,13 +1858,13 @@
         <v>1.5446</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2207</v>
+        <v>-0.1518</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2763</v>
+        <v>-0.4831</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0555</v>
+        <v>0.3313</v>
       </c>
       <c r="V18" t="n">
         <v>-0.8995</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1758</v>
+        <v>-1.7607</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2676</v>
+        <v>0.371</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4434</v>
+        <v>-2.1317</v>
       </c>
       <c r="G19" t="n">
         <v>0.0394</v>
@@ -1936,13 +1936,13 @@
         <v>0.3862</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1806</v>
+        <v>-0.7655</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7174</v>
+        <v>-0.6139</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4632</v>
+        <v>-0.1515</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2277</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2751</v>
+        <v>-1.9911</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4393</v>
+        <v>-0.2324</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8358</v>
+        <v>-1.7587</v>
       </c>
       <c r="G20" t="n">
         <v>-1.3377</v>
@@ -2014,13 +2014,13 @@
         <v>0.7723</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7941</v>
+        <v>-0.5102</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8554</v>
+        <v>-0.6485</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0612</v>
+        <v>0.1384</v>
       </c>
       <c r="V20" t="n">
         <v>0.243</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Y. BOUBACAR</t>
+          <t>L. NVE MALEVA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5461</v>
+        <v>-2.8177</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1121</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.434</v>
+        <v>-2.2103</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.9817</v>
+        <v>0.8129</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.2967</v>
+        <v>0.6344</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.1786</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1394</v>
+        <v>0.7442</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2614</v>
+        <v>0.7035</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1221</v>
+        <v>0.0407</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8423</v>
+        <v>0.0687</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0352</v>
+        <v>-0.0692</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8071</v>
+        <v>0.1379</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3862</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1931</v>
+        <v>-0.9654</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5792</v>
+        <v>0.7723</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2924</v>
+        <v>-0.0828</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2204</v>
+        <v>-0.3863</v>
       </c>
       <c r="U21" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.3035</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.243</v>
+        <v>-3.3548</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.243</v>
+        <v>-3.3548</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. NVE MALEVA</t>
+          <t>Y. BOUBACAR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8066</v>
+        <v>-2.8178</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-1.4223</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1992</v>
+        <v>-1.3955</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8129</v>
+        <v>-2.9817</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6344</v>
+        <v>-2.2967</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1786</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7442</v>
+        <v>-1.1394</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7035</v>
+        <v>-1.2614</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0407</v>
+        <v>0.1221</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0687</v>
+        <v>-1.8423</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0692</v>
+        <v>-1.0352</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1379</v>
+        <v>-0.8071</v>
       </c>
       <c r="P22" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-0.1931</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-0.9654</v>
-      </c>
       <c r="R22" t="n">
-        <v>0.7723</v>
+        <v>0.5792</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0717</v>
+        <v>0.0207</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3863</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3146</v>
+        <v>0.1106</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.3548</v>
+        <v>-0.243</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.3548</v>
+        <v>-0.243</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.9114</v>
+        <v>-5.3487</v>
       </c>
       <c r="E23" t="n">
         <v>-3.5075</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4039</v>
+        <v>-1.8412</v>
       </c>
       <c r="G23" t="n">
         <v>-3.4135</v>
@@ -2248,13 +2248,13 @@
         <v>1.3515</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.7489</v>
+        <v>-1.1862</v>
       </c>
       <c r="T23" t="n">
         <v>-1.0761</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6727</v>
+        <v>-0.1101</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9421</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-12.468</v>
+        <v>-10.3996</v>
       </c>
       <c r="E24" t="n">
-        <v>4.678600000000001</v>
+        <v>4.678799999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-17.1467</v>
+        <v>-15.0783</v>
       </c>
       <c r="G24" t="n">
         <v>-1.6564</v>
@@ -2317,7 +2317,7 @@
         <v>-5.245299999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>9.999999999998899e-05</v>
+        <v>0.0001000000000000445</v>
       </c>
       <c r="Q24" t="n">
         <v>-8.688600000000001</v>
@@ -2326,13 +2326,13 @@
         <v>8.688499999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.7577</v>
+        <v>-4.6894</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.2436</v>
+        <v>-5.243399999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.5142</v>
+        <v>0.5542</v>
       </c>
       <c r="V24" t="n">
         <v>-4.0539</v>
